--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487575_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487575_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4129</v>
+        <v>4.0734</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8387</v>
+        <v>4.4458</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4259</v>
+        <v>-0.3724</v>
       </c>
       <c r="G2" t="n">
         <v>2.5127</v>
@@ -610,13 +610,13 @@
         <v>1.9585</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1426</v>
+        <v>-0.482</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5087</v>
+        <v>0.1159</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6513</v>
+        <v>-0.5978</v>
       </c>
       <c r="V2" t="n">
         <v>2.0427</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1083</v>
+        <v>1.7954</v>
       </c>
       <c r="E3" t="n">
-        <v>1.842</v>
+        <v>0.7163</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2663</v>
+        <v>1.0792</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3517</v>
@@ -688,13 +688,13 @@
         <v>1.5668</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8931</v>
+        <v>0.5803</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4703</v>
+        <v>0.3446</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4228</v>
+        <v>0.2357</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9557</v>
+        <v>1.5107</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5035</v>
+        <v>1.2724</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4522</v>
+        <v>0.2384</v>
       </c>
       <c r="G4" t="n">
         <v>0.5043</v>
@@ -766,13 +766,13 @@
         <v>1.9585</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1361</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2535</v>
+        <v>0.0223</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3896</v>
+        <v>-0.6034</v>
       </c>
       <c r="V4" t="n">
         <v>0.6083</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ TAPIA</t>
+          <t>P. BAZAL GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0494</v>
+        <v>0.4255</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5552</v>
+        <v>3.0828</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5058</v>
+        <v>-2.6573</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7171999999999999</v>
+        <v>4.006</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3842</v>
+        <v>0.9089</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.667</v>
+        <v>3.0971</v>
       </c>
       <c r="J5" t="n">
-        <v>0.962</v>
+        <v>4.1873</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5634</v>
+        <v>0.4287</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6014</v>
+        <v>3.7586</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2449</v>
+        <v>-0.1813</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8208</v>
+        <v>0.4802</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0656</v>
+        <v>-0.6615</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3917</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5668</v>
+        <v>0.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7654</v>
+        <v>-0.0678</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5587</v>
+        <v>-0.1253</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2067</v>
+        <v>0.0575</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3905</v>
+        <v>-3.3169</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3905</v>
+        <v>-3.3169</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. BAZAL GARCIA</t>
+          <t>S. RODRÍGUEZ TAPIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0818</v>
+        <v>0.3275</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4953</v>
+        <v>-1.2317</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.5771</v>
+        <v>1.5593</v>
       </c>
       <c r="G6" t="n">
-        <v>4.006</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9089</v>
+        <v>2.3842</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0971</v>
+        <v>-1.667</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1873</v>
+        <v>0.962</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4287</v>
+        <v>1.5634</v>
       </c>
       <c r="L6" t="n">
-        <v>3.7586</v>
+        <v>-0.6014</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1813</v>
+        <v>-0.2449</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4802</v>
+        <v>0.8208</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6615</v>
+        <v>-1.0656</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1958</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.3885</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7128</v>
+        <v>-0.2353</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1377</v>
+        <v>-0.1532</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.3169</v>
+        <v>0.3905</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.3169</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CANEDA FONTOIRA</t>
+          <t>H. SANCHEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9364</v>
+        <v>-0.1723</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.699</v>
+        <v>0.5687</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2375</v>
+        <v>-0.7409</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6375</v>
+        <v>1.8151</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.375</v>
+        <v>3.3972</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2625</v>
+        <v>-1.5821</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5802</v>
+        <v>1.8402</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5802</v>
+        <v>2.7765</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.9362</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0573</v>
+        <v>-0.0251</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2052</v>
+        <v>0.6208</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2625</v>
+        <v>-0.6459</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5875</v>
+        <v>2.546</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6111</v>
+        <v>-1.7293</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1188</v>
+        <v>-0.2923</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4923</v>
+        <v>-1.437</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2754</v>
+        <v>-1.8249</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2754</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. MARTINEZ CARRO</t>
+          <t>M. CANEDA FONTOIRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1656</v>
+        <v>-0.8562</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5491</v>
+        <v>-0.699</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3835</v>
+        <v>-0.1573</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3885</v>
+        <v>-0.6375</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8803</v>
+        <v>-0.375</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2688</v>
+        <v>-0.2625</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3323</v>
+        <v>-0.5802</v>
       </c>
       <c r="K8" t="n">
-        <v>1.674</v>
+        <v>-0.5802</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0063</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0563</v>
+        <v>-0.0573</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2062</v>
+        <v>0.2052</v>
       </c>
       <c r="O8" t="n">
         <v>-0.2625</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5875</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7771</v>
+        <v>-0.5309</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2376</v>
+        <v>-0.1188</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5395</v>
+        <v>-0.4121</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. SANCHEZ EXPOSITO</t>
+          <t>T. MARTINEZ CARRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3028</v>
+        <v>-1.1924</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4282</v>
+        <v>-1.5491</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8746</v>
+        <v>0.3567</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8151</v>
+        <v>-0.3885</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3972</v>
+        <v>1.8803</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5821</v>
+        <v>-2.2688</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8402</v>
+        <v>-0.3323</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7765</v>
+        <v>1.674</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9362</v>
+        <v>-2.0063</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0251</v>
+        <v>-0.0563</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6208</v>
+        <v>0.2062</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6459</v>
+        <v>-0.2625</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5668</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>2.546</v>
+        <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.8598</v>
+        <v>-0.8038</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2892</v>
+        <v>-0.2376</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.5706</v>
+        <v>-0.5662</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8249</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0048</v>
+        <v>-2.3816</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8148</v>
+        <v>-3.4054</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.0238</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1747</v>
@@ -1234,13 +1234,13 @@
         <v>2.546</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.2253</v>
+        <v>-1.6021</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7369</v>
+        <v>-0.3276</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4883</v>
+        <v>-1.2745</v>
       </c>
       <c r="V10" t="n">
         <v>2.7662</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3276</v>
+        <v>-4.0309</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4722</v>
+        <v>-2.1487</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8555</v>
+        <v>-1.8822</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4775</v>
@@ -1312,13 +1312,13 @@
         <v>2.1543</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3052</v>
+        <v>-1.0085</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3694</v>
+        <v>-0.0459</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9359</v>
+        <v>-0.9626</v>
       </c>
       <c r="V11" t="n">
         <v>0.2178</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.391500000000002</v>
+        <v>-0.5009000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1609999999999996</v>
+        <v>1.0521</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5528</v>
+        <v>-1.552700000000001</v>
       </c>
       <c r="G12" t="n">
         <v>4.5254</v>
@@ -1366,10 +1366,10 @@
         <v>6.958299999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>7.113899999999999</v>
+        <v>7.1139</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1557000000000004</v>
+        <v>-0.1556999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-2.433</v>
@@ -1378,7 +1378,7 @@
         <v>5.4945</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.927300000000001</v>
+        <v>-7.927299999999999</v>
       </c>
       <c r="P12" t="n">
         <v>0.9793000000000003</v>
@@ -1390,16 +1390,16 @@
         <v>16.647</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.5046</v>
+        <v>-6.6137</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7909</v>
+        <v>-0.9000000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.7137</v>
+        <v>-5.7136</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6083000000000007</v>
+        <v>0.6082999999999998</v>
       </c>
       <c r="W12" t="n">
         <v>10.6616</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.342</v>
+        <v>13.1613</v>
       </c>
       <c r="E13" t="n">
-        <v>11.8499</v>
+        <v>11.2359</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4921</v>
+        <v>1.9254</v>
       </c>
       <c r="G13" t="n">
         <v>7.6392</v>
@@ -1468,13 +1468,13 @@
         <v>2.9377</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7972</v>
+        <v>1.6165</v>
       </c>
       <c r="T13" t="n">
-        <v>1.772</v>
+        <v>1.158</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0252</v>
+        <v>0.4585</v>
       </c>
       <c r="V13" t="n">
         <v>2.9263</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.913</v>
+        <v>6.0032</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1298</v>
+        <v>4.6181</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7832</v>
+        <v>1.3851</v>
       </c>
       <c r="G14" t="n">
         <v>-1.6739</v>
@@ -1546,13 +1546,13 @@
         <v>2.7419</v>
       </c>
       <c r="S14" t="n">
-        <v>3.27</v>
+        <v>2.3602</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0096</v>
+        <v>1.498</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2604</v>
+        <v>0.8622</v>
       </c>
       <c r="V14" t="n">
         <v>4.5335</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3621</v>
+        <v>1.5179</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8095</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5526</v>
+        <v>0.6061</v>
       </c>
       <c r="G15" t="n">
         <v>-0.07969999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4626</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4205</v>
+        <v>0.5228</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0421</v>
+        <v>0.0956</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>N. LAGARES COUCE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-0.6918</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4667</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3121</v>
+        <v>-0.0392</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5037</v>
+        <v>-1.5549</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-1.5397</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3537</v>
+        <v>-0.0152</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3785</v>
+        <v>-0.9455</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2977</v>
+        <v>-0.3845</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0808</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8822</v>
+        <v>-0.6093</v>
       </c>
       <c r="N16" t="n">
         <v>-1.1551</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2729</v>
+        <v>0.5458</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1751</v>
+        <v>1.3709</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1751</v>
+        <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3082</v>
+        <v>0.7087</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0882</v>
+        <v>0.2929</v>
       </c>
       <c r="U16" t="n">
-        <v>0.22</v>
+        <v>0.4158</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8249</v>
+        <v>-1.2166</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8249</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. LAGARES COUCE</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2468</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8573</v>
+        <v>0.4667</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3895</v>
+        <v>-1.3121</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5549</v>
+        <v>-0.5037</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5397</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0152</v>
+        <v>0.3537</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9455</v>
+        <v>0.3785</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3845</v>
+        <v>0.2977</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5610000000000001</v>
+        <v>0.0808</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6093</v>
+        <v>-0.8822</v>
       </c>
       <c r="N17" t="n">
         <v>-1.1551</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5458</v>
+        <v>0.2729</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1537</v>
+        <v>0.3082</v>
       </c>
       <c r="T17" t="n">
         <v>0.0882</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0655</v>
+        <v>0.22</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2166</v>
+        <v>-1.8249</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2166</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. FOLCH CLARAMUNT</t>
+          <t>J. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.333</v>
+        <v>-0.9363</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3746</v>
+        <v>-0.6936</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0417</v>
+        <v>-0.2426</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2732</v>
+        <v>-1.2991</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8639</v>
+        <v>-0.8445</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4093</v>
+        <v>-0.4546</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-1.2428</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0204</v>
+        <v>-0.6414</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6822</v>
+        <v>-0.6014</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.0563</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8843</v>
+        <v>-0.2031</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2729</v>
+        <v>0.1468</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5668</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>1.507</v>
+        <v>0.2833</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2457</v>
+        <v>0.0365</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2614</v>
+        <v>0.2469</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GONZALEZ VAZQUEZ</t>
+          <t>D. MARTIN MACEIRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3677</v>
+        <v>-1.742</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2053</v>
+        <v>-0.9444</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1624</v>
+        <v>-0.7976</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2991</v>
+        <v>-0.5099</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8445</v>
+        <v>-0.9797</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4546</v>
+        <v>0.4698</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2428</v>
+        <v>-0.2671</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6414</v>
+        <v>-0.8474</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6014</v>
+        <v>0.5803</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0563</v>
+        <v>-0.2428</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2031</v>
+        <v>-0.1323</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1468</v>
+        <v>-0.1105</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1958</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1482</v>
+        <v>0.3186</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4752</v>
+        <v>0.3976</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3271</v>
+        <v>-0.079</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2754</v>
+        <v>-1.159</v>
       </c>
       <c r="W19" t="n">
-        <v>1.492</v>
+        <v>0.8837</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2166</v>
+        <v>-2.0427</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. GONZALEZ VAZQUEZ</t>
+          <t>X. FOLCH CLARAMUNT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9921</v>
+        <v>-1.8981</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1174</v>
+        <v>-1.8863</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1254</v>
+        <v>-0.0118</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4827</v>
+        <v>-1.2732</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3256</v>
+        <v>-0.8639</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8083</v>
+        <v>-0.4093</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4254</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2569</v>
+        <v>0.0204</v>
       </c>
       <c r="L20" t="n">
         <v>-0.6822</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0573</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0687</v>
+        <v>-0.8843</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1261</v>
+        <v>0.2729</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7626</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1957</v>
+        <v>0.9419</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2664</v>
+        <v>0.734</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0708</v>
+        <v>0.2079</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MARTIN MACEIRA</t>
+          <t>S. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8446</v>
+        <v>-2.087</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4561</v>
+        <v>-2.3221</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3885</v>
+        <v>0.2351</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5099</v>
+        <v>-0.4827</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9797</v>
+        <v>0.3256</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4698</v>
+        <v>-0.8083</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2671</v>
+        <v>-0.4254</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8474</v>
+        <v>0.2569</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5803</v>
+        <v>-0.6822</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2428</v>
+        <v>-0.0573</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1323</v>
+        <v>0.0687</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1105</v>
+        <v>-0.1261</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3917</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5668</v>
+        <v>0.1958</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7839</v>
+        <v>0.1007</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1141</v>
+        <v>0.0618</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6698</v>
+        <v>0.039</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.159</v>
+        <v>0.0576</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.0427</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ROZAS RAMOS</t>
+          <t>L. PORTILLA QUEIRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9297</v>
+        <v>-4.8595</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.6614</v>
+        <v>-3.417</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7317</v>
+        <v>-1.4425</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.8189</v>
+        <v>-0.9685</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.9902</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8287</v>
+        <v>-0.3077</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.173</v>
+        <v>-0.3903</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.586</v>
+        <v>-0.5972</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5869</v>
+        <v>0.2069</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6459</v>
+        <v>-0.5782</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4041</v>
+        <v>-0.0635</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2417</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="P22" t="n">
         <v>-1.1751</v>
@@ -2170,28 +2170,28 @@
         <v>1.7626</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8903</v>
+        <v>0.6586</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4493</v>
+        <v>0.577</v>
       </c>
       <c r="U22" t="n">
-        <v>0.441</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-3.3745</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. PORTILLA QUEIRO</t>
+          <t>M. ROZAS RAMOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6662</v>
+        <v>-4.8661</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.031</v>
+        <v>-5.7637</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6352</v>
+        <v>0.8976</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9685</v>
+        <v>-3.8189</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-2.9902</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3077</v>
+        <v>-0.8287</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3903</v>
+        <v>-3.173</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5972</v>
+        <v>-2.586</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2069</v>
+        <v>-0.5869</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5782</v>
+        <v>-0.6459</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0635</v>
+        <v>-0.4041</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.2417</v>
       </c>
       <c r="P23" t="n">
         <v>-1.1751</v>
@@ -2248,22 +2248,22 @@
         <v>1.7626</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1482</v>
+        <v>0.954</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0371</v>
+        <v>0.347</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1111</v>
+        <v>0.607</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.3745</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.7086</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.391700000000004</v>
+        <v>2.756300000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5528</v>
+        <v>1.552700000000003</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1610000000000003</v>
+        <v>1.2035</v>
       </c>
       <c r="G24" t="n">
         <v>-4.5253</v>
@@ -2302,10 +2302,10 @@
         <v>2.4331</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.4942</v>
+        <v>-5.494199999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>7.9273</v>
+        <v>7.927299999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-6.958299999999999</v>
@@ -2317,7 +2317,7 @@
         <v>0.1557999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9793000000000001</v>
+        <v>-0.9792999999999994</v>
       </c>
       <c r="Q24" t="n">
         <v>-16.6471</v>
@@ -2326,16 +2326,16 @@
         <v>15.6677</v>
       </c>
       <c r="S24" t="n">
-        <v>7.504399999999999</v>
+        <v>8.8691</v>
       </c>
       <c r="T24" t="n">
-        <v>5.713500000000001</v>
+        <v>5.713799999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>1.791</v>
+        <v>3.1555</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.608299999999999</v>
+        <v>-0.6083</v>
       </c>
       <c r="W24" t="n">
         <v>10.0532</v>
